--- a/60_Threshold_OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/60_Threshold_OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TGTTTATATTTTGTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TGTT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TGTT</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TATATTT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.005397840863654539</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TTTAT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TAT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.8148740503798481</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TTATATTTTGTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;ATATTTTG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.4584166333466613</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.3794482207117153</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>TGTTTATATTTTGTTTA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;TTTATATTTTGTT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9512195121951219</v>
       </c>
     </row>

--- a/60_Threshold_OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/60_Threshold_OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.005397840863654539</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.8148740503798481</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -586,6 +601,11 @@
       <c r="I4" t="n">
         <v>0.4584166333466613</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.3794482207117153</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -663,6 +688,11 @@
       </c>
       <c r="I6" t="n">
         <v>0.9512195121951219</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ambiguous DR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/60_Threshold_OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/60_Threshold_OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Ambiguous DR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -606,6 +617,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -650,6 +664,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -693,6 +710,9 @@
         <is>
           <t>Ambiguous DR</t>
         </is>
+      </c>
+      <c r="K6" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
